--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0063.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0063.xlsx
@@ -30344,7 +30344,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Rover... hãy nhận lấy lòng tốt của ta... Hãy đập tan cơn ác mộng này...</t>
+          <t>Vận Mệnh Giả... hãy nhận lấy lòng tốt của ta... Hãy đập tan cơn ác mộng này...</t>
         </is>
       </c>
     </row>
@@ -32099,7 +32099,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Ừ hừm. Đã xác nhận. Hòm Septimont có thể dùng để nạp vào Quả Cầu Sonoro của Bức Tranh Biến Hình.</t>
+          <t>Ừ hừm. Đã xác nhận. Hòm Septimont có thể dùng để nạp vào Sonoro Sphere của Bức Tranh Biến Hình.</t>
         </is>
       </c>
     </row>
@@ -32489,7 +32489,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Vì mấy con Plushies có thể di chuyển qua nó, ta nghi bức tranh Morph Painting này có liên hệ với Order of the Deep.</t>
+          <t>Vì mấy con Plushies có thể di chuyển qua nó, tao nghi bức tranh Morph Painting này có liên hệ với Order of the Deep.</t>
         </is>
       </c>
     </row>
